--- a/Excel/PCA_loadings_pinv_25.xlsx
+++ b/Excel/PCA_loadings_pinv_25.xlsx
@@ -579,79 +579,79 @@
         <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>5.6191941148625e-05</v>
+        <v>2.484336683840617</v>
       </c>
       <c r="C4" t="n">
-        <v>6.570619049840439e-07</v>
+        <v>0.02904977049624424</v>
       </c>
       <c r="D4" t="n">
-        <v>1.542215371455395e-05</v>
+        <v>0.6818383816917477</v>
       </c>
       <c r="E4" t="n">
-        <v>-6.122587585959209e-05</v>
+        <v>-2.706895086538076</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.991904062892735e-05</v>
+        <v>-1.322769220290283</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.999394119003912e-05</v>
+        <v>-0.8839645069670047</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.001060025369342237</v>
+        <v>-46.86543758816187</v>
       </c>
       <c r="I4" t="n">
-        <v>-2.995380303227744e-06</v>
+        <v>-0.1324306122416987</v>
       </c>
       <c r="J4" t="n">
-        <v>4.80012634582121e-05</v>
+        <v>2.122213563765612</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0002500307751561888</v>
+        <v>11.05426532902034</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.0001575084030435355</v>
+        <v>-6.963701479171704</v>
       </c>
       <c r="M4" t="n">
-        <v>4.758692797049328e-05</v>
+        <v>2.10389512111148</v>
       </c>
       <c r="N4" t="n">
-        <v>-6.827667124316742e-05</v>
+        <v>-3.018622164542722</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.0002978653415392127</v>
+        <v>-13.16910894523643</v>
       </c>
       <c r="P4" t="n">
-        <v>-2.058973008746331e-05</v>
+        <v>-0.9103052986079899</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.0001767232651282166</v>
+        <v>-7.813221637687646</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.0001922453200769034</v>
+        <v>-8.499476814664266</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.0008694253495804429</v>
+        <v>-38.43870216390348</v>
       </c>
       <c r="T4" t="n">
-        <v>1.145291407089102e-05</v>
+        <v>0.5063518714886963</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0004803277723550065</v>
+        <v>-21.23606838875249</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.0004006286171700018</v>
+        <v>-17.71243971798799</v>
       </c>
       <c r="W4" t="n">
-        <v>-1.698770673647544e-05</v>
+        <v>-0.7510540151678682</v>
       </c>
       <c r="X4" t="n">
-        <v>-3.430428680152775e-05</v>
+        <v>-1.516648052584824</v>
       </c>
       <c r="Y4" t="n">
-        <v>9.747075508041294e-05</v>
+        <v>4.309339871485001</v>
       </c>
       <c r="Z4" t="n">
-        <v>-0.0002208412807559666</v>
+        <v>-9.763750528518647</v>
       </c>
     </row>
     <row r="5">
@@ -659,79 +659,79 @@
         <v>1</v>
       </c>
       <c r="B5" t="n">
-        <v>0.0001296996182706544</v>
+        <v>9.37117972750481</v>
       </c>
       <c r="C5" t="n">
-        <v>-1.073805046341425e-06</v>
+        <v>-0.07758557978612036</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.038376229166145e-05</v>
+        <v>-0.7502574331389352</v>
       </c>
       <c r="E5" t="n">
-        <v>2.833716892655199e-05</v>
+        <v>2.047443982643299</v>
       </c>
       <c r="F5" t="n">
-        <v>2.895425724957221e-06</v>
+        <v>0.2092030432933472</v>
       </c>
       <c r="G5" t="n">
-        <v>1.50454588220306e-05</v>
+        <v>1.087078748449347</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.0008809275954133454</v>
+        <v>-63.64961542377121</v>
       </c>
       <c r="I5" t="n">
-        <v>7.159032853184824e-08</v>
+        <v>0.005172612258757487</v>
       </c>
       <c r="J5" t="n">
-        <v>-2.881166960478522e-05</v>
+        <v>-2.081728055301556</v>
       </c>
       <c r="K5" t="n">
-        <v>-7.557761938129805e-05</v>
+        <v>-5.460705775719041</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0001137079646325938</v>
+        <v>8.215735614557779</v>
       </c>
       <c r="M5" t="n">
-        <v>-3.631463592304758e-05</v>
+        <v>-2.623839487820405</v>
       </c>
       <c r="N5" t="n">
-        <v>4.314546173878096e-05</v>
+        <v>3.117386787805057</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.0001852716935640737</v>
+        <v>-13.38642597378349</v>
       </c>
       <c r="P5" t="n">
-        <v>1.263033816554807e-05</v>
+        <v>0.9125791621184008</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.0001261159575727862</v>
+        <v>-9.112249678751231</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.0001350999726343675</v>
+        <v>-9.761371248569571</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.000789497258488828</v>
+        <v>-57.04350407749045</v>
       </c>
       <c r="T5" t="n">
-        <v>-5.218139481913067e-06</v>
+        <v>-0.3770259587514764</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0004154221256778823</v>
+        <v>-30.01547309403524</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.0003391977378284807</v>
+        <v>-24.50803639005709</v>
       </c>
       <c r="W5" t="n">
-        <v>7.477419861508488e-06</v>
+        <v>0.5402656257166688</v>
       </c>
       <c r="X5" t="n">
-        <v>8.665294449098998e-06</v>
+        <v>0.6260930660936924</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.001608642819235394</v>
+        <v>-116.2291853855481</v>
       </c>
       <c r="Z5" t="n">
-        <v>-0.0001469117275136086</v>
+        <v>-10.61480535536557</v>
       </c>
     </row>
     <row r="6">
@@ -739,79 +739,79 @@
         <v>2</v>
       </c>
       <c r="B6" t="n">
-        <v>-8.374249388852722e-05</v>
+        <v>-1.996369780283153</v>
       </c>
       <c r="C6" t="n">
-        <v>-3.542949550205737e-07</v>
+        <v>-0.008446174799276215</v>
       </c>
       <c r="D6" t="n">
-        <v>-3.60199240690275e-06</v>
+        <v>-0.08586929354554738</v>
       </c>
       <c r="E6" t="n">
-        <v>2.027624013165505e-05</v>
+        <v>0.4833731499623496</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.496240065040973e-06</v>
+        <v>-0.03566944702974068</v>
       </c>
       <c r="G6" t="n">
-        <v>9.401486490574899e-06</v>
+        <v>0.2241256815746098</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0003969705769860629</v>
+        <v>9.463535497419608</v>
       </c>
       <c r="I6" t="n">
-        <v>-8.460034969131944e-07</v>
+        <v>-0.0201682053737215</v>
       </c>
       <c r="J6" t="n">
-        <v>3.814534522164116e-05</v>
+        <v>0.9093616743766987</v>
       </c>
       <c r="K6" t="n">
-        <v>-6.037529746682709e-07</v>
+        <v>-0.014393101248987</v>
       </c>
       <c r="L6" t="n">
-        <v>-9.735915406882568e-06</v>
+        <v>-0.232098262174539</v>
       </c>
       <c r="M6" t="n">
-        <v>2.28727839794925e-05</v>
+        <v>0.5452731654778035</v>
       </c>
       <c r="N6" t="n">
-        <v>2.224261062649773e-05</v>
+        <v>0.5302502185861923</v>
       </c>
       <c r="O6" t="n">
-        <v>-2.095635256539812e-05</v>
+        <v>-0.499586613962225</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.0001088064803671514</v>
+        <v>-2.59387987170644</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.731492536106623e-05</v>
+        <v>0.412777218991149</v>
       </c>
       <c r="R6" t="n">
-        <v>1.452210813139452e-05</v>
+        <v>0.3461981662274184</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0003211180707925306</v>
+        <v>7.655258192888031</v>
       </c>
       <c r="T6" t="n">
-        <v>-4.738986169791947e-06</v>
+        <v>-0.1129745286920405</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0001787930399066255</v>
+        <v>4.262316599618745</v>
       </c>
       <c r="V6" t="n">
-        <v>0.0001496139368951576</v>
+        <v>3.56670464966411</v>
       </c>
       <c r="W6" t="n">
-        <v>7.63046353806744e-06</v>
+        <v>0.1819055787522615</v>
       </c>
       <c r="X6" t="n">
-        <v>-7.269584493223357e-06</v>
+        <v>-0.1733024432829112</v>
       </c>
       <c r="Y6" t="n">
-        <v>-0.0007039960689422753</v>
+        <v>-16.78283523948193</v>
       </c>
       <c r="Z6" t="n">
-        <v>7.838053347555667e-06</v>
+        <v>0.1868543927069477</v>
       </c>
     </row>
     <row r="7">
@@ -819,79 +819,79 @@
         <v>3</v>
       </c>
       <c r="B7" t="n">
-        <v>-0.0001572033613127472</v>
+        <v>-4.702301243461553</v>
       </c>
       <c r="C7" t="n">
-        <v>-4.445478265971291e-07</v>
+        <v>-0.01329741158413861</v>
       </c>
       <c r="D7" t="n">
-        <v>1.780728142288736e-06</v>
+        <v>0.05326552872551341</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.34199337092084e-05</v>
+        <v>-0.4014199851772652</v>
       </c>
       <c r="F7" t="n">
-        <v>1.231148158395526e-05</v>
+        <v>0.3682637233558157</v>
       </c>
       <c r="G7" t="n">
-        <v>1.345592847496076e-06</v>
+        <v>0.04024966684642157</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0004000773007202906</v>
+        <v>11.9671995111797</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.608263943504993e-06</v>
+        <v>-0.07801896016980904</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0001047090107693912</v>
+        <v>3.132078776375403</v>
       </c>
       <c r="K7" t="n">
-        <v>-6.004558602573831e-06</v>
+        <v>-0.1796096670423178</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.000140073740993776</v>
+        <v>-4.189916303004131</v>
       </c>
       <c r="M7" t="n">
-        <v>8.518601304369651e-05</v>
+        <v>2.548102608722154</v>
       </c>
       <c r="N7" t="n">
-        <v>-2.018492625692345e-05</v>
+        <v>-0.6037759183041788</v>
       </c>
       <c r="O7" t="n">
-        <v>-6.004508787829711e-05</v>
+        <v>-1.796081769728547</v>
       </c>
       <c r="P7" t="n">
-        <v>5.263866985377408e-05</v>
+        <v>1.574539377788041</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.02152047308162e-06</v>
+        <v>0.0903803796500682</v>
       </c>
       <c r="R7" t="n">
-        <v>-2.325451839528871e-06</v>
+        <v>-0.06955942280950569</v>
       </c>
       <c r="S7" t="n">
-        <v>0.000320014629671247</v>
+        <v>9.572347426053113</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.003969064845929e-05</v>
+        <v>-0.3003094172159486</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0001793147767458969</v>
+        <v>5.363702726341621</v>
       </c>
       <c r="V7" t="n">
-        <v>0.00015044687889264</v>
+        <v>4.500199867128377</v>
       </c>
       <c r="W7" t="n">
-        <v>9.971861215074642e-06</v>
+        <v>0.2982804884049885</v>
       </c>
       <c r="X7" t="n">
-        <v>-3.80275653715498e-05</v>
+        <v>-1.137488832549236</v>
       </c>
       <c r="Y7" t="n">
-        <v>-0.0008969707615553093</v>
+        <v>-26.83038512782814</v>
       </c>
       <c r="Z7" t="n">
-        <v>-1.404526012566791e-05</v>
+        <v>-0.4201248853851036</v>
       </c>
     </row>
     <row r="8">
@@ -899,79 +899,79 @@
         <v>4</v>
       </c>
       <c r="B8" t="n">
-        <v>8.152181706601992e-06</v>
+        <v>0.3695887965701247</v>
       </c>
       <c r="C8" t="n">
-        <v>6.737748839794124e-07</v>
+        <v>0.03054638101693033</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.015876305651483e-05</v>
+        <v>-0.9139213582991703</v>
       </c>
       <c r="E8" t="n">
-        <v>2.942314569176246e-05</v>
+        <v>1.33393309900335</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.365501444083932e-05</v>
+        <v>-0.6190662249653436</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.33540021441551e-06</v>
+        <v>-0.06054194765868943</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.0002191059794155844</v>
+        <v>-9.933428641309559</v>
       </c>
       <c r="I8" t="n">
-        <v>3.946677926063799e-06</v>
+        <v>0.1789273102146991</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0001755521465789694</v>
+        <v>7.958864132883304</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.0003331258267172655</v>
+        <v>-15.10265323246549</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0001938080419137014</v>
+        <v>8.786516733120322</v>
       </c>
       <c r="M8" t="n">
-        <v>-3.796983134800028e-05</v>
+        <v>-1.721407198580089</v>
       </c>
       <c r="N8" t="n">
-        <v>3.878988850091406e-05</v>
+        <v>1.758585459219071</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.0001487267938312929</v>
+        <v>-6.742705048554536</v>
       </c>
       <c r="P8" t="n">
-        <v>1.035292911607666e-06</v>
+        <v>0.04693622824780455</v>
       </c>
       <c r="Q8" t="n">
-        <v>-6.786420067065202e-05</v>
+        <v>-3.076703778050793</v>
       </c>
       <c r="R8" t="n">
-        <v>-7.668644437959689e-05</v>
+        <v>-3.476670627758862</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.000157469169540395</v>
+        <v>-7.139050988055993</v>
       </c>
       <c r="T8" t="n">
-        <v>-3.576803792890502e-06</v>
+        <v>-0.1621586290589214</v>
       </c>
       <c r="U8" t="n">
-        <v>-9.388687052247952e-05</v>
+        <v>-4.256472284227385</v>
       </c>
       <c r="V8" t="n">
-        <v>-8.073125471229512e-05</v>
+        <v>-3.660046886657185</v>
       </c>
       <c r="W8" t="n">
-        <v>-1.188066208086778e-05</v>
+        <v>-0.5386238627836476</v>
       </c>
       <c r="X8" t="n">
-        <v>1.661427339363869e-05</v>
+        <v>0.7532277285317416</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.0003831076240452127</v>
+        <v>17.36863711134392</v>
       </c>
       <c r="Z8" t="n">
-        <v>-9.541576262559375e-05</v>
+        <v>-4.325786415439444</v>
       </c>
     </row>
     <row r="9">
@@ -979,79 +979,79 @@
         <v>5</v>
       </c>
       <c r="B9" t="n">
-        <v>-8.533035600520342e-05</v>
+        <v>-7.826761588675491</v>
       </c>
       <c r="C9" t="n">
-        <v>1.363164974519729e-06</v>
+        <v>0.1250336663420004</v>
       </c>
       <c r="D9" t="n">
-        <v>7.410205897576571e-06</v>
+        <v>0.6796867796940675</v>
       </c>
       <c r="E9" t="n">
-        <v>3.900735336979596e-05</v>
+        <v>3.577873916428818</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.865878572998089e-05</v>
+        <v>-3.545902224968919</v>
       </c>
       <c r="G9" t="n">
-        <v>-5.097339180098034e-06</v>
+        <v>-0.4675435608965671</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0005966154130486762</v>
+        <v>54.72339290107121</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.32646684917491e-06</v>
+        <v>-0.1216676018923496</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.648711619984112e-05</v>
+        <v>-1.512248791896225</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0003742826864287879</v>
+        <v>34.33035429113248</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0003643719365271451</v>
+        <v>33.42130995712759</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.218569831256672e-05</v>
+        <v>-2.034940195962038</v>
       </c>
       <c r="N9" t="n">
-        <v>4.396119027229943e-05</v>
+        <v>4.032255008929036</v>
       </c>
       <c r="O9" t="n">
-        <v>-8.312706979247733e-05</v>
+        <v>-7.624669429379084</v>
       </c>
       <c r="P9" t="n">
-        <v>1.391185220008114e-05</v>
+        <v>1.276037690740279</v>
       </c>
       <c r="Q9" t="n">
-        <v>9.550775838752983e-06</v>
+        <v>0.8760264104868505</v>
       </c>
       <c r="R9" t="n">
-        <v>2.149327032334587e-06</v>
+        <v>0.1971428580134811</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0005609831518861387</v>
+        <v>51.45509277857366</v>
       </c>
       <c r="T9" t="n">
-        <v>1.622027034109219e-05</v>
+        <v>1.487772872479851</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0002877268701276795</v>
+        <v>26.39118973097669</v>
       </c>
       <c r="V9" t="n">
-        <v>0.0002321811715539165</v>
+        <v>21.29636814149735</v>
       </c>
       <c r="W9" t="n">
-        <v>-2.060231595196322e-05</v>
+        <v>-1.889707516522558</v>
       </c>
       <c r="X9" t="n">
-        <v>1.734478605916776e-05</v>
+        <v>1.590916898124833</v>
       </c>
       <c r="Y9" t="n">
-        <v>-0.0008249229066765889</v>
+        <v>-75.66445543952774</v>
       </c>
       <c r="Z9" t="n">
-        <v>-1.905719714077332e-05</v>
+        <v>-1.74798448702278</v>
       </c>
     </row>
     <row r="10">
@@ -1059,79 +1059,79 @@
         <v>6</v>
       </c>
       <c r="B10" t="n">
-        <v>0.0001009821122954982</v>
+        <v>3.95585959459009</v>
       </c>
       <c r="C10" t="n">
-        <v>2.311513986582289e-07</v>
+        <v>0.009055093594291831</v>
       </c>
       <c r="D10" t="n">
-        <v>1.411624935603943e-05</v>
+        <v>0.552988041003818</v>
       </c>
       <c r="E10" t="n">
-        <v>-6.237567155995586e-05</v>
+        <v>-2.443496112335227</v>
       </c>
       <c r="F10" t="n">
-        <v>3.469513723546636e-06</v>
+        <v>0.1359142608513665</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.157213360096082e-05</v>
+        <v>-1.23680248697478</v>
       </c>
       <c r="H10" t="n">
-        <v>6.510636216969343e-05</v>
+        <v>2.550467816558952</v>
       </c>
       <c r="I10" t="n">
-        <v>6.99150623652763e-06</v>
+        <v>0.2738843186947003</v>
       </c>
       <c r="J10" t="n">
-        <v>5.47991964157724e-05</v>
+        <v>2.146696300853914</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0002949302061808386</v>
+        <v>11.55355596485094</v>
       </c>
       <c r="L10" t="n">
-        <v>-8.373488923900708e-05</v>
+        <v>-3.280219213762955</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.331086613516737e-05</v>
+        <v>-0.5214380677542356</v>
       </c>
       <c r="N10" t="n">
-        <v>-7.907819981444539e-05</v>
+        <v>-3.097798692737681</v>
       </c>
       <c r="O10" t="n">
-        <v>0.0003590997840679927</v>
+        <v>14.06732632076183</v>
       </c>
       <c r="P10" t="n">
-        <v>-3.330554947122468e-06</v>
+        <v>-0.1304707085580618</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.0001365311488987487</v>
+        <v>5.34845274132373</v>
       </c>
       <c r="R10" t="n">
-        <v>0.0001596184730524775</v>
+        <v>6.252872451813502</v>
       </c>
       <c r="S10" t="n">
-        <v>6.462395769627768e-05</v>
+        <v>2.531570169032729</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.900515655961271e-06</v>
+        <v>-0.07445054298629003</v>
       </c>
       <c r="U10" t="n">
-        <v>3.222482977493052e-05</v>
+        <v>1.262371118522055</v>
       </c>
       <c r="V10" t="n">
-        <v>2.565551410967796e-05</v>
+        <v>1.005025636104035</v>
       </c>
       <c r="W10" t="n">
-        <v>1.305437134571179e-06</v>
+        <v>0.05113901756001066</v>
       </c>
       <c r="X10" t="n">
-        <v>7.29047677121603e-06</v>
+        <v>0.2855961499414634</v>
       </c>
       <c r="Y10" t="n">
-        <v>-0.0008325005665014391</v>
+        <v>-32.61226447570752</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.0002061251800702559</v>
+        <v>8.074719895752025</v>
       </c>
     </row>
     <row r="11">
@@ -1139,79 +1139,79 @@
         <v>7</v>
       </c>
       <c r="B11" t="n">
-        <v>-0.000198365920229398</v>
+        <v>-10.740475681567</v>
       </c>
       <c r="C11" t="n">
-        <v>-8.04685778746346e-07</v>
+        <v>-0.04356952055036698</v>
       </c>
       <c r="D11" t="n">
-        <v>1.167542878104825e-07</v>
+        <v>0.006321633209479472</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.830490746540158e-05</v>
+        <v>-2.615457752685003</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.495794039339409e-05</v>
+        <v>-0.8098941333057417</v>
       </c>
       <c r="G11" t="n">
-        <v>2.664548322807823e-05</v>
+        <v>1.442713366811307</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.0005630867547930856</v>
+        <v>-30.48819872624105</v>
       </c>
       <c r="I11" t="n">
-        <v>1.346098899004079e-06</v>
+        <v>0.07288420547752414</v>
       </c>
       <c r="J11" t="n">
-        <v>1.185769778115118e-05</v>
+        <v>0.6420322327067727</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0002191314595807011</v>
+        <v>11.86482088239231</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.0002152092207540153</v>
+        <v>-11.65245219181015</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.0001235788894626852</v>
+        <v>-6.691149646542518</v>
       </c>
       <c r="N11" t="n">
-        <v>-5.600514698182768e-05</v>
+        <v>-3.032385394150698</v>
       </c>
       <c r="O11" t="n">
-        <v>4.809737769600161e-06</v>
+        <v>0.2604221102565316</v>
       </c>
       <c r="P11" t="n">
-        <v>3.641158176302588e-06</v>
+        <v>0.1971496454637462</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.545537208858866e-05</v>
+        <v>-1.919722708709308</v>
       </c>
       <c r="R11" t="n">
-        <v>-3.321118895564727e-05</v>
+        <v>-1.798211945487106</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.0005095358060522664</v>
+        <v>-27.58869531350523</v>
       </c>
       <c r="T11" t="n">
-        <v>5.391547495820344e-06</v>
+        <v>0.2919240598279405</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0002667235349831757</v>
+        <v>-14.44168251217477</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.0002172714654711416</v>
+        <v>-11.76411194267915</v>
       </c>
       <c r="W11" t="n">
-        <v>-3.567070719738087e-06</v>
+        <v>-0.1931381977078789</v>
       </c>
       <c r="X11" t="n">
-        <v>5.508350667216515e-05</v>
+        <v>2.982483398275484</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.655729189121102e-05</v>
+        <v>0.8964906406529467</v>
       </c>
       <c r="Z11" t="n">
-        <v>-2.408955015835017e-05</v>
+        <v>-1.304322977235365</v>
       </c>
     </row>
     <row r="12">
@@ -1219,79 +1219,79 @@
         <v>8</v>
       </c>
       <c r="B12" t="n">
-        <v>8.741435875379215e-05</v>
+        <v>9.398620964019146</v>
       </c>
       <c r="C12" t="n">
-        <v>-1.597906011328101e-06</v>
+        <v>-0.171803730539283</v>
       </c>
       <c r="D12" t="n">
-        <v>1.208859477753893e-05</v>
+        <v>1.299742078091713</v>
       </c>
       <c r="E12" t="n">
-        <v>1.614539737047744e-05</v>
+        <v>1.735921562108385</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.511508901232037e-05</v>
+        <v>-3.775505722968798</v>
       </c>
       <c r="G12" t="n">
-        <v>6.398792744597796e-05</v>
+        <v>6.879856866899611</v>
       </c>
       <c r="H12" t="n">
-        <v>0.0003737609857375786</v>
+        <v>40.18605050893039</v>
       </c>
       <c r="I12" t="n">
-        <v>2.531193752920004e-06</v>
+        <v>0.2721490040005128</v>
       </c>
       <c r="J12" t="n">
-        <v>3.875426464933388e-05</v>
+        <v>4.166782773117093</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0001938735721143911</v>
+        <v>20.84490746395324</v>
       </c>
       <c r="L12" t="n">
-        <v>3.819981420298855e-05</v>
+        <v>4.10716934503933</v>
       </c>
       <c r="M12" t="n">
-        <v>5.93910127734794e-05</v>
+        <v>6.385605587971377</v>
       </c>
       <c r="N12" t="n">
-        <v>1.737404419096819e-05</v>
+        <v>1.868023266325697</v>
       </c>
       <c r="O12" t="n">
-        <v>4.979649017548732e-05</v>
+        <v>5.354021274881145</v>
       </c>
       <c r="P12" t="n">
-        <v>4.767651594899311e-06</v>
+        <v>0.5126085790455615</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.019214989534271e-05</v>
+        <v>4.32138138379899</v>
       </c>
       <c r="R12" t="n">
-        <v>4.197589338987735e-05</v>
+        <v>4.513165997232841</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0002500751213306817</v>
+        <v>26.88758816544181</v>
       </c>
       <c r="T12" t="n">
-        <v>1.223287963694447e-05</v>
+        <v>1.315255304107819</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0001556575732908427</v>
+        <v>16.73599798015083</v>
       </c>
       <c r="V12" t="n">
-        <v>0.0001359818619235029</v>
+        <v>14.62050395862613</v>
       </c>
       <c r="W12" t="n">
-        <v>-1.915565908317898e-05</v>
+        <v>-2.059579016599038</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.57680392486848e-05</v>
+        <v>-2.770529205235984</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.0003122377596119738</v>
+        <v>33.57119350967213</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.779826614288309e-05</v>
+        <v>5.13917613328909</v>
       </c>
     </row>
     <row r="13">
@@ -1299,79 +1299,79 @@
         <v>9</v>
       </c>
       <c r="B13" t="n">
-        <v>-8.25543378558363e-06</v>
+        <v>-0.2419636764584359</v>
       </c>
       <c r="C13" t="n">
-        <v>-4.355922533246349e-07</v>
+        <v>-0.01276704601946995</v>
       </c>
       <c r="D13" t="n">
-        <v>1.126869211186658e-05</v>
+        <v>0.3302811509464946</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.867085788206072e-05</v>
+        <v>-1.719620899740408</v>
       </c>
       <c r="F13" t="n">
-        <v>2.993881400735999e-05</v>
+        <v>0.8774954404789465</v>
       </c>
       <c r="G13" t="n">
-        <v>-6.01072173053003e-06</v>
+        <v>-0.1761720057191061</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0005304453800326088</v>
+        <v>15.54715568516864</v>
       </c>
       <c r="I13" t="n">
-        <v>3.645398340591057e-08</v>
+        <v>0.001068452618667675</v>
       </c>
       <c r="J13" t="n">
-        <v>-2.172512403032178e-05</v>
+        <v>-0.6367552594354715</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.0006364972872981649</v>
+        <v>-18.65549742030701</v>
       </c>
       <c r="L13" t="n">
-        <v>-4.039648684508001e-05</v>
+        <v>-1.184005919847384</v>
       </c>
       <c r="M13" t="n">
-        <v>-9.233753976074025e-06</v>
+        <v>-0.2706378753185461</v>
       </c>
       <c r="N13" t="n">
-        <v>-7.823005553887167e-05</v>
+        <v>-2.292893667294209</v>
       </c>
       <c r="O13" t="n">
-        <v>-9.768514292399413e-05</v>
+        <v>-2.863115001725446</v>
       </c>
       <c r="P13" t="n">
-        <v>-3.694979599955208e-06</v>
+        <v>-0.108298470033784</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.435912054106973e-06</v>
+        <v>-0.07139567119664406</v>
       </c>
       <c r="R13" t="n">
-        <v>-1.06860388473794e-05</v>
+        <v>-0.3132038016954173</v>
       </c>
       <c r="S13" t="n">
-        <v>0.0004306523600976825</v>
+        <v>12.6222595966665</v>
       </c>
       <c r="T13" t="n">
-        <v>1.77141828859831e-05</v>
+        <v>0.5191960747155524</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0002392885331691195</v>
+        <v>7.013457405599905</v>
       </c>
       <c r="V13" t="n">
-        <v>0.0002000654236495722</v>
+        <v>5.863842736283072</v>
       </c>
       <c r="W13" t="n">
-        <v>-4.616991049024057e-05</v>
+        <v>-1.353222807441453</v>
       </c>
       <c r="X13" t="n">
-        <v>9.944723162630569e-06</v>
+        <v>0.2914761162512488</v>
       </c>
       <c r="Y13" t="n">
-        <v>-0.0005060736878579191</v>
+        <v>-14.83283050332323</v>
       </c>
       <c r="Z13" t="n">
-        <v>-2.897870212210638e-05</v>
+        <v>-0.8493549202348168</v>
       </c>
     </row>
     <row r="14">
@@ -1379,79 +1379,79 @@
         <v>10</v>
       </c>
       <c r="B14" t="n">
-        <v>9.443263018601713e-05</v>
+        <v>0.6843233261414979</v>
       </c>
       <c r="C14" t="n">
-        <v>-8.688811758161146e-09</v>
+        <v>-6.296506356820448e-05</v>
       </c>
       <c r="D14" t="n">
-        <v>1.623626556328773e-05</v>
+        <v>0.1176590679778693</v>
       </c>
       <c r="E14" t="n">
-        <v>-7.873459200870918e-05</v>
+        <v>-0.5705646213566187</v>
       </c>
       <c r="F14" t="n">
-        <v>-3.536706609267389e-06</v>
+        <v>-0.02562939129909622</v>
       </c>
       <c r="G14" t="n">
-        <v>1.337390000981608e-05</v>
+        <v>0.09691641247493563</v>
       </c>
       <c r="H14" t="n">
-        <v>0.001192908922150222</v>
+        <v>8.64463268450392</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.293342619712741e-06</v>
+        <v>-0.00937244384297058</v>
       </c>
       <c r="J14" t="n">
-        <v>2.106570102573294e-05</v>
+        <v>0.1526564553484938</v>
       </c>
       <c r="K14" t="n">
-        <v>4.902111274296381e-05</v>
+        <v>0.3552404593343027</v>
       </c>
       <c r="L14" t="n">
-        <v>9.851237079657394e-05</v>
+        <v>0.7138879126505665</v>
       </c>
       <c r="M14" t="n">
-        <v>-4.587812843622273e-05</v>
+        <v>-0.3324642487112672</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.0001090656257295452</v>
+        <v>-0.7903640046869981</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.0004669130277523002</v>
+        <v>-3.383570652864952</v>
       </c>
       <c r="P14" t="n">
-        <v>4.156584174107577e-07</v>
+        <v>0.003012144744683552</v>
       </c>
       <c r="Q14" t="n">
-        <v>-9.509982556897641e-05</v>
+        <v>-0.6891582795125384</v>
       </c>
       <c r="R14" t="n">
-        <v>-0.0001296203643617243</v>
+        <v>-0.9393176775968307</v>
       </c>
       <c r="S14" t="n">
-        <v>0.001008625397102938</v>
+        <v>7.309188415239947</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.043733658388172e-05</v>
+        <v>-0.07563606851859021</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0005478712565369705</v>
+        <v>3.970249264816296</v>
       </c>
       <c r="V14" t="n">
-        <v>0.0004536738489626825</v>
+        <v>3.28763052235233</v>
       </c>
       <c r="W14" t="n">
-        <v>2.994383341475424e-05</v>
+        <v>0.2169934654943622</v>
       </c>
       <c r="X14" t="n">
-        <v>3.494120428099664e-05</v>
+        <v>0.2532078274835764</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.0001539335831251267</v>
+        <v>1.115507864194422</v>
       </c>
       <c r="Z14" t="n">
-        <v>-0.0002058633059471993</v>
+        <v>-1.491826098444675</v>
       </c>
     </row>
     <row r="15">
@@ -1459,79 +1459,79 @@
         <v>11</v>
       </c>
       <c r="B15" t="n">
-        <v>-2.903952598334199e-05</v>
+        <v>-3.498712447825473</v>
       </c>
       <c r="C15" t="n">
-        <v>1.790558845670941e-06</v>
+        <v>0.2157284015416263</v>
       </c>
       <c r="D15" t="n">
-        <v>2.95384148774299e-05</v>
+        <v>3.558819103313845</v>
       </c>
       <c r="E15" t="n">
-        <v>2.89195087686959e-05</v>
+        <v>3.484252648341235</v>
       </c>
       <c r="F15" t="n">
-        <v>-4.30873757165508e-05</v>
+        <v>-5.191212069029763</v>
       </c>
       <c r="G15" t="n">
-        <v>3.193493761413234e-05</v>
+        <v>3.847554667909736</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.0002237775487605671</v>
+        <v>-26.96095300734511</v>
       </c>
       <c r="I15" t="n">
-        <v>3.550098762238376e-06</v>
+        <v>0.4277196100782791</v>
       </c>
       <c r="J15" t="n">
-        <v>-3.621456060432937e-05</v>
+        <v>-4.363168119602872</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.0004372958493369267</v>
+        <v>-52.6858610686396</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.0002072549675602037</v>
+        <v>-24.97029515194216</v>
       </c>
       <c r="M15" t="n">
-        <v>1.238921982861353e-05</v>
+        <v>1.492666156399425</v>
       </c>
       <c r="N15" t="n">
-        <v>3.807208049263233e-05</v>
+        <v>4.58696405756054</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.216175941002405e-05</v>
+        <v>-1.46526148738501</v>
       </c>
       <c r="P15" t="n">
-        <v>2.992866229450364e-06</v>
+        <v>0.3605836520079822</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.646754210070032e-05</v>
+        <v>-1.984026687138774</v>
       </c>
       <c r="R15" t="n">
-        <v>-1.632640271273977e-05</v>
+        <v>-1.967022066132886</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.0001152512892777191</v>
+        <v>-13.88559581362263</v>
       </c>
       <c r="T15" t="n">
-        <v>-2.250143450441927e-06</v>
+        <v>-0.2710996351651906</v>
       </c>
       <c r="U15" t="n">
-        <v>-8.483033461393287e-05</v>
+        <v>-10.22044739425892</v>
       </c>
       <c r="V15" t="n">
-        <v>-7.819368232209917e-05</v>
+        <v>-9.420856588312368</v>
       </c>
       <c r="W15" t="n">
-        <v>2.080138966326494e-05</v>
+        <v>2.506173171996001</v>
       </c>
       <c r="X15" t="n">
-        <v>-8.10636991560858e-06</v>
+        <v>-0.9766639216730486</v>
       </c>
       <c r="Y15" t="n">
-        <v>-0.000338024466143255</v>
+        <v>-40.725541045104</v>
       </c>
       <c r="Z15" t="n">
-        <v>-1.934844841435486e-05</v>
+        <v>-2.331121291450887</v>
       </c>
     </row>
     <row r="16">
@@ -1539,79 +1539,79 @@
         <v>12</v>
       </c>
       <c r="B16" t="n">
-        <v>0.0001269229144379032</v>
+        <v>12.60452920905047</v>
       </c>
       <c r="C16" t="n">
-        <v>1.47589840829455e-06</v>
+        <v>0.146569314763418</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.400176860009659e-05</v>
+        <v>-1.390495184261054</v>
       </c>
       <c r="E16" t="n">
-        <v>2.956667182073381e-05</v>
+        <v>2.936222984078864</v>
       </c>
       <c r="F16" t="n">
-        <v>3.11917051718548e-05</v>
+        <v>3.097602672140686</v>
       </c>
       <c r="G16" t="n">
-        <v>3.503944096842347e-05</v>
+        <v>3.479715692877313</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0002974847597937563</v>
+        <v>29.54277689472839</v>
       </c>
       <c r="I16" t="n">
-        <v>-4.827849264423641e-06</v>
+        <v>-0.4794466573653407</v>
       </c>
       <c r="J16" t="n">
-        <v>4.632653173996339e-05</v>
+        <v>4.60062018790199</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0001548236739523599</v>
+        <v>15.37531287575169</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.0003399661104725106</v>
+        <v>-33.7615377689308</v>
       </c>
       <c r="M16" t="n">
-        <v>-4.357747162663335e-05</v>
+        <v>-4.327615044194403</v>
       </c>
       <c r="N16" t="n">
-        <v>3.456603184945165e-05</v>
+        <v>3.432702124883332</v>
       </c>
       <c r="O16" t="n">
-        <v>0.0001194536054197023</v>
+        <v>11.86276304248942</v>
       </c>
       <c r="P16" t="n">
-        <v>1.683613854073169e-06</v>
+        <v>0.1671972322287805</v>
       </c>
       <c r="Q16" t="n">
-        <v>6.498325086385123e-05</v>
+        <v>6.453391708186631</v>
       </c>
       <c r="R16" t="n">
-        <v>7.179514608109069e-05</v>
+        <v>7.129871070600756</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0003126325680644166</v>
+        <v>31.04708360440508</v>
       </c>
       <c r="T16" t="n">
-        <v>5.398563110023161e-07</v>
+        <v>0.05361234156066714</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0001514525003690381</v>
+        <v>15.04052655219482</v>
       </c>
       <c r="V16" t="n">
-        <v>0.0001188467243572681</v>
+        <v>11.80249457078162</v>
       </c>
       <c r="W16" t="n">
-        <v>-1.707150901596086e-05</v>
+        <v>-1.695346620326182</v>
       </c>
       <c r="X16" t="n">
-        <v>2.485080568452779e-05</v>
+        <v>2.467897207578814</v>
       </c>
       <c r="Y16" t="n">
-        <v>-0.0002738151281738577</v>
+        <v>-27.19218035791186</v>
       </c>
       <c r="Z16" t="n">
-        <v>8.083665669121343e-05</v>
+        <v>8.02777028040013</v>
       </c>
     </row>
     <row r="17">
@@ -1619,79 +1619,79 @@
         <v>13</v>
       </c>
       <c r="B17" t="n">
-        <v>5.219194023476254e-05</v>
+        <v>3.351230080110217</v>
       </c>
       <c r="C17" t="n">
-        <v>-9.542686902561763e-07</v>
+        <v>-0.06127332927094077</v>
       </c>
       <c r="D17" t="n">
-        <v>2.272072508500317e-05</v>
+        <v>1.458891487924837</v>
       </c>
       <c r="E17" t="n">
-        <v>1.987504161458552e-05</v>
+        <v>1.276170937555573</v>
       </c>
       <c r="F17" t="n">
-        <v>-5.34563793131201e-05</v>
+        <v>-3.432419364409612</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.249893859083645e-05</v>
+        <v>-1.444650638336361</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.0001624314996668623</v>
+        <v>-10.42968177064294</v>
       </c>
       <c r="I17" t="n">
-        <v>-6.604859700846554e-06</v>
+        <v>-0.4240962187805767</v>
       </c>
       <c r="J17" t="n">
-        <v>5.855132884846064e-05</v>
+        <v>3.759564668122714</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.0002809872816405144</v>
+        <v>-18.04211581570769</v>
       </c>
       <c r="L17" t="n">
-        <v>3.62214666714433e-05</v>
+        <v>2.32577037966106</v>
       </c>
       <c r="M17" t="n">
-        <v>-5.186311702661089e-05</v>
+        <v>-3.330116432653513</v>
       </c>
       <c r="N17" t="n">
-        <v>2.64777659675586e-05</v>
+        <v>1.700130046238419</v>
       </c>
       <c r="O17" t="n">
-        <v>0.0003549511818575912</v>
+        <v>22.79131743831088</v>
       </c>
       <c r="P17" t="n">
-        <v>1.658845106548948e-06</v>
+        <v>0.1065139865332656</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.0001188231824889643</v>
+        <v>7.629603758363747</v>
       </c>
       <c r="R17" t="n">
-        <v>0.0001423550029636654</v>
+        <v>9.140575457439338</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0001768372434570586</v>
+        <v>-11.354670604147</v>
       </c>
       <c r="T17" t="n">
-        <v>3.23488331177635e-06</v>
+        <v>0.2077109647832398</v>
       </c>
       <c r="U17" t="n">
-        <v>-8.418385896324281e-05</v>
+        <v>-5.405422353497082</v>
       </c>
       <c r="V17" t="n">
-        <v>-6.54657667419098e-05</v>
+        <v>-4.203538817222093</v>
       </c>
       <c r="W17" t="n">
-        <v>1.21877326333906e-05</v>
+        <v>0.782570949185642</v>
       </c>
       <c r="X17" t="n">
-        <v>2.379953335180335e-05</v>
+        <v>1.528161469038978</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.888748161274387e-05</v>
+        <v>1.212759982354431</v>
       </c>
       <c r="Z17" t="n">
-        <v>0.0001936837347743422</v>
+        <v>12.43637916284133</v>
       </c>
     </row>
     <row r="18">
@@ -1699,79 +1699,79 @@
         <v>14</v>
       </c>
       <c r="B18" t="n">
-        <v>1.726689309996235e-05</v>
+        <v>1.092855809847147</v>
       </c>
       <c r="C18" t="n">
-        <v>-9.406293732157098e-07</v>
+        <v>-0.05953429314008863</v>
       </c>
       <c r="D18" t="n">
-        <v>1.133053032522688e-05</v>
+        <v>0.7171316705841326</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0001128538301869793</v>
+        <v>7.142742082744308</v>
       </c>
       <c r="F18" t="n">
-        <v>-8.241844722875912e-06</v>
+        <v>-0.5216426508873404</v>
       </c>
       <c r="G18" t="n">
-        <v>-4.089007327619973e-05</v>
+        <v>-2.588013598408732</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0007336268409613498</v>
+        <v>46.43269352297071</v>
       </c>
       <c r="I18" t="n">
-        <v>2.416557188609308e-06</v>
+        <v>0.1529486832466372</v>
       </c>
       <c r="J18" t="n">
-        <v>-3.723017676985895e-07</v>
+        <v>-0.02356371511020247</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0001208617393168835</v>
+        <v>7.64957848734133</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.0003387035972576028</v>
+        <v>-21.43722046208317</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.043367684475896e-05</v>
+        <v>-1.29328781541968</v>
       </c>
       <c r="N18" t="n">
-        <v>0.0001360163749049915</v>
+        <v>8.608745342240942</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.0003445031083908163</v>
+        <v>-21.80428299032816</v>
       </c>
       <c r="P18" t="n">
-        <v>4.207700224887218e-06</v>
+        <v>0.2663136680259758</v>
       </c>
       <c r="Q18" t="n">
-        <v>-8.081585105789452e-05</v>
+        <v>-5.114995028060955</v>
       </c>
       <c r="R18" t="n">
-        <v>-0.0001058394027096094</v>
+        <v>-6.698785096561876</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0005816283975129825</v>
+        <v>36.81241145782943</v>
       </c>
       <c r="T18" t="n">
-        <v>1.367559682412236e-06</v>
+        <v>0.08655555667047778</v>
       </c>
       <c r="U18" t="n">
-        <v>0.000327553353841288</v>
+        <v>20.73149950648403</v>
       </c>
       <c r="V18" t="n">
-        <v>0.0002753916670819541</v>
+        <v>17.43008320093618</v>
       </c>
       <c r="W18" t="n">
-        <v>-8.184458616733491e-06</v>
+        <v>-0.5180105707477092</v>
       </c>
       <c r="X18" t="n">
-        <v>1.749015129916309e-05</v>
+        <v>1.106986262771185</v>
       </c>
       <c r="Y18" t="n">
-        <v>7.86747096536803e-05</v>
+        <v>4.97947795444754</v>
       </c>
       <c r="Z18" t="n">
-        <v>-0.000158246798039705</v>
+        <v>-10.0157527834458</v>
       </c>
     </row>
     <row r="19">
@@ -1779,79 +1779,79 @@
         <v>15</v>
       </c>
       <c r="B19" t="n">
-        <v>-2.881120003764596e-05</v>
+        <v>-0.2482648762899355</v>
       </c>
       <c r="C19" t="n">
-        <v>6.207263032881211e-08</v>
+        <v>0.0005348771960014834</v>
       </c>
       <c r="D19" t="n">
-        <v>4.832918102140966e-05</v>
+        <v>0.4164504821665462</v>
       </c>
       <c r="E19" t="n">
-        <v>4.313394886437757e-05</v>
+        <v>0.3716833892624763</v>
       </c>
       <c r="F19" t="n">
-        <v>7.353924675709809e-05</v>
+        <v>0.6336845384694387</v>
       </c>
       <c r="G19" t="n">
-        <v>1.133451552173079e-05</v>
+        <v>0.09766903461612343</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.0005260963488549951</v>
+        <v>-4.533349697145984</v>
       </c>
       <c r="I19" t="n">
-        <v>-4.37435281939207e-07</v>
+        <v>-0.003769361082272269</v>
       </c>
       <c r="J19" t="n">
-        <v>3.296969220177602e-05</v>
+        <v>0.2840984250949675</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0001206805190557431</v>
+        <v>1.039898862068609</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0001862301324702345</v>
+        <v>1.604737072345819</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.098702083642414e-05</v>
+        <v>-0.180844259345018</v>
       </c>
       <c r="N19" t="n">
-        <v>5.867942177877235e-05</v>
+        <v>0.5056380633099967</v>
       </c>
       <c r="O19" t="n">
-        <v>2.518671725956566e-05</v>
+        <v>0.2170328634845368</v>
       </c>
       <c r="P19" t="n">
-        <v>-5.083220331136698e-06</v>
+        <v>-0.04380189179955118</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.443829970416408e-05</v>
+        <v>-0.2105837814760577</v>
       </c>
       <c r="R19" t="n">
-        <v>-2.093624043694804e-05</v>
+        <v>-0.1804066868184466</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0004424162115458069</v>
+        <v>-3.812281539282184</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.289803413691835e-05</v>
+        <v>-0.1111418075332312</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0002410380068208232</v>
+        <v>-2.077014177346113</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.0001998539775830067</v>
+        <v>-1.722133161960153</v>
       </c>
       <c r="W19" t="n">
-        <v>-1.162431215835757e-05</v>
+        <v>-0.1001661998174113</v>
       </c>
       <c r="X19" t="n">
-        <v>4.955940539337013e-06</v>
+        <v>0.04270512728699639</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.0002213662184603783</v>
+        <v>1.90750321989463</v>
       </c>
       <c r="Z19" t="n">
-        <v>-1.150054110009031e-05</v>
+        <v>-0.09909966991136891</v>
       </c>
     </row>
     <row r="20">
@@ -1859,79 +1859,79 @@
         <v>16</v>
       </c>
       <c r="B20" t="n">
-        <v>2.221286794021345e-06</v>
+        <v>0.02979343306674697</v>
       </c>
       <c r="C20" t="n">
-        <v>3.159200599969656e-08</v>
+        <v>0.0004237338099381884</v>
       </c>
       <c r="D20" t="n">
-        <v>7.812222297156485e-07</v>
+        <v>0.01047829225561291</v>
       </c>
       <c r="E20" t="n">
-        <v>1.897284625512538e-05</v>
+        <v>0.2544769214444426</v>
       </c>
       <c r="F20" t="n">
-        <v>4.61020476055864e-05</v>
+        <v>0.6183525122797676</v>
       </c>
       <c r="G20" t="n">
-        <v>7.058820086417405e-07</v>
+        <v>0.009467777161461126</v>
       </c>
       <c r="H20" t="n">
-        <v>-7.551059185017134e-05</v>
+        <v>-1.012800224704734</v>
       </c>
       <c r="I20" t="n">
-        <v>5.48655872669688e-07</v>
+        <v>0.007358951605464945</v>
       </c>
       <c r="J20" t="n">
-        <v>3.941822518103936e-05</v>
+        <v>0.5287044683748895</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.270234508085339e-05</v>
+        <v>-0.1703726276929807</v>
       </c>
       <c r="L20" t="n">
-        <v>1.073814017321706e-05</v>
+        <v>0.1440273544925213</v>
       </c>
       <c r="M20" t="n">
-        <v>7.120235764846477e-07</v>
+        <v>0.009550152112296302</v>
       </c>
       <c r="N20" t="n">
-        <v>2.450694131863003e-05</v>
+        <v>0.3287040276890338</v>
       </c>
       <c r="O20" t="n">
-        <v>-2.236167418471291e-05</v>
+        <v>-0.2999302228221099</v>
       </c>
       <c r="P20" t="n">
-        <v>1.656581745637049e-07</v>
+        <v>0.002221921882895887</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.303047202021452e-05</v>
+        <v>-0.1747736928915632</v>
       </c>
       <c r="R20" t="n">
-        <v>-1.421459610795589e-05</v>
+        <v>-0.1906559832134611</v>
       </c>
       <c r="S20" t="n">
-        <v>-6.256224739852837e-05</v>
+        <v>-0.8391280835010277</v>
       </c>
       <c r="T20" t="n">
-        <v>4.383657786812152e-05</v>
+        <v>0.5879664670515883</v>
       </c>
       <c r="U20" t="n">
-        <v>-3.436862871812638e-05</v>
+        <v>-0.4609757920793328</v>
       </c>
       <c r="V20" t="n">
-        <v>-2.859755895710435e-05</v>
+        <v>-0.3835702174766686</v>
       </c>
       <c r="W20" t="n">
-        <v>4.393199670423423e-05</v>
+        <v>0.5892462904020357</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.041291609430711e-06</v>
+        <v>-0.01396652244637594</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.205084080650124e-06</v>
+        <v>0.01616342022708756</v>
       </c>
       <c r="Z20" t="n">
-        <v>-1.63662049104058e-05</v>
+        <v>-0.2195148469199172</v>
       </c>
     </row>
     <row r="21">
@@ -1939,79 +1939,79 @@
         <v>17</v>
       </c>
       <c r="B21" t="n">
-        <v>-1.148878168254853e-08</v>
+        <v>-5.446187817498203e-05</v>
       </c>
       <c r="C21" t="n">
-        <v>2.328056231345179e-09</v>
+        <v>1.1036010462823e-05</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.504148965401556e-09</v>
+        <v>-1.661120729110071e-05</v>
       </c>
       <c r="E21" t="n">
-        <v>6.0509159825481e-07</v>
+        <v>0.002868400307252036</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.143201107664254e-08</v>
+        <v>-5.419276053405e-05</v>
       </c>
       <c r="G21" t="n">
-        <v>6.804998679391411e-09</v>
+        <v>3.225868671767958e-05</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.0002832372715488458</v>
+        <v>-1.34266924062271</v>
       </c>
       <c r="I21" t="n">
-        <v>5.643825260518911e-10</v>
+        <v>2.6754214007018e-06</v>
       </c>
       <c r="J21" t="n">
-        <v>-2.502246160870999e-08</v>
+        <v>-0.0001186174734104667</v>
       </c>
       <c r="K21" t="n">
-        <v>2.762175564427943e-08</v>
+        <v>0.0001309392703596389</v>
       </c>
       <c r="L21" t="n">
-        <v>1.060142016377021e-08</v>
+        <v>5.025539429191541e-05</v>
       </c>
       <c r="M21" t="n">
-        <v>0.0001391705685212109</v>
+        <v>0.6597297048216322</v>
       </c>
       <c r="N21" t="n">
-        <v>-6.402233278033169e-07</v>
+        <v>-0.003034940156957035</v>
       </c>
       <c r="O21" t="n">
-        <v>3.290280911837369e-05</v>
+        <v>0.1559737865420819</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.117253104565247e-10</v>
+        <v>-5.296271101911364e-07</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.074846121693824e-05</v>
+        <v>-0.05095243355894366</v>
       </c>
       <c r="R21" t="n">
-        <v>-2.397966872418512e-05</v>
+        <v>-0.1136741764959878</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.0002285168246476898</v>
+        <v>-1.083270255151827</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.740640445449282e-08</v>
+        <v>-8.251401280337462e-05</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0001212593907689869</v>
+        <v>-0.5748228445778197</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.0001150311078416015</v>
+        <v>-0.545298044177199</v>
       </c>
       <c r="W21" t="n">
-        <v>-1.86338881201375e-08</v>
+        <v>-8.833282525006312e-05</v>
       </c>
       <c r="X21" t="n">
-        <v>0.0001391654368709638</v>
+        <v>0.6597053785424577</v>
       </c>
       <c r="Y21" t="n">
-        <v>-7.91277802898783e-09</v>
+        <v>-3.751004805306366e-05</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.717494324472756e-06</v>
+        <v>0.008141678486746334</v>
       </c>
     </row>
     <row r="22">
@@ -2019,79 +2019,79 @@
         <v>18</v>
       </c>
       <c r="B22" t="n">
-        <v>-3.720506962683223e-10</v>
+        <v>-3.369229497343987e-07</v>
       </c>
       <c r="C22" t="n">
-        <v>1.150204423423998e-08</v>
+        <v>1.041606075880218e-05</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.070459338551106e-11</v>
+        <v>-1.874973754474594e-08</v>
       </c>
       <c r="E22" t="n">
-        <v>-7.408826811665106e-05</v>
+        <v>-0.06709310853847336</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.126514828984941e-10</v>
+        <v>-1.925736611485937e-07</v>
       </c>
       <c r="G22" t="n">
-        <v>1.384441482213474e-10</v>
+        <v>1.253727269204766e-07</v>
       </c>
       <c r="H22" t="n">
-        <v>4.318003505879189e-05</v>
+        <v>0.0391031245909723</v>
       </c>
       <c r="I22" t="n">
-        <v>1.881514514890837e-11</v>
+        <v>1.703868446053734e-08</v>
       </c>
       <c r="J22" t="n">
-        <v>-4.056921915785902e-10</v>
+        <v>-3.673881295741614e-07</v>
       </c>
       <c r="K22" t="n">
-        <v>1.890111560216498e-10</v>
+        <v>1.711653809363946e-07</v>
       </c>
       <c r="L22" t="n">
-        <v>7.616299099857094e-10</v>
+        <v>6.897194376951183e-07</v>
       </c>
       <c r="M22" t="n">
-        <v>3.153906582092455e-06</v>
+        <v>0.002856125564972414</v>
       </c>
       <c r="N22" t="n">
-        <v>7.408777387512194e-05</v>
+        <v>0.06709266096153124</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.0005578868785183826</v>
+        <v>-0.5052131173277071</v>
       </c>
       <c r="P22" t="n">
-        <v>4.023103662858706e-12</v>
+        <v>3.643256605780163e-09</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.354928159366675e-05</v>
+        <v>0.02132583938228108</v>
       </c>
       <c r="R22" t="n">
-        <v>0.0006898361382365756</v>
+        <v>0.6247041815526839</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.0006609486339766992</v>
+        <v>-0.5985441361368259</v>
       </c>
       <c r="T22" t="n">
-        <v>-2.121770478206029e-10</v>
+        <v>-1.921440199314833e-07</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0003840636235666724</v>
+        <v>-0.3478016565465779</v>
       </c>
       <c r="V22" t="n">
-        <v>0.0001946619411979686</v>
+        <v>0.1762826299103362</v>
       </c>
       <c r="W22" t="n">
-        <v>-2.102520143895889e-10</v>
+        <v>-1.904007422503453e-07</v>
       </c>
       <c r="X22" t="n">
-        <v>3.153712434784886e-06</v>
+        <v>0.002855949748387194</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.416057786569941e-09</v>
+        <v>1.282358466654837e-06</v>
       </c>
       <c r="Z22" t="n">
-        <v>-0.0001555020584931389</v>
+        <v>-0.140820088708369</v>
       </c>
     </row>
     <row r="23">
@@ -2099,79 +2099,79 @@
         <v>19</v>
       </c>
       <c r="B23" t="n">
-        <v>7.247733923366507e-12</v>
+        <v>2.104548231099058e-08</v>
       </c>
       <c r="C23" t="n">
-        <v>4.315454465902731e-08</v>
+        <v>0.0001253092716863255</v>
       </c>
       <c r="D23" t="n">
-        <v>3.16203370535527e-12</v>
+        <v>9.181698422697696e-09</v>
       </c>
       <c r="E23" t="n">
-        <v>5.134404617873124e-05</v>
+        <v>0.149089396792933</v>
       </c>
       <c r="F23" t="n">
-        <v>4.118231995666978e-11</v>
+        <v>1.195824616515907e-07</v>
       </c>
       <c r="G23" t="n">
-        <v>-4.574503923011912e-12</v>
+        <v>-1.328313795701782e-08</v>
       </c>
       <c r="H23" t="n">
-        <v>0.000662852333461504</v>
+        <v>1.924746137352563</v>
       </c>
       <c r="I23" t="n">
-        <v>4.14765342618686e-13</v>
+        <v>1.204368508403359e-09</v>
       </c>
       <c r="J23" t="n">
-        <v>2.777948752656607e-11</v>
+        <v>8.066421703005356e-08</v>
       </c>
       <c r="K23" t="n">
-        <v>1.3782290285217e-11</v>
+        <v>4.002008978728248e-08</v>
       </c>
       <c r="L23" t="n">
-        <v>-3.630898210094781e-11</v>
+        <v>-1.054315905754821e-07</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.060434231329689e-07</v>
+        <v>-0.0003079217779985207</v>
       </c>
       <c r="N23" t="n">
-        <v>-5.13439947087952e-05</v>
+        <v>-0.149089247337987</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.0002492406923557508</v>
+        <v>-0.7237284017356064</v>
       </c>
       <c r="P23" t="n">
-        <v>-6.126468494381354e-13</v>
+        <v>-1.77896265268208e-09</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.0003765038644922936</v>
+        <v>-1.093266663323804</v>
       </c>
       <c r="R23" t="n">
-        <v>0.0001449255559924828</v>
+        <v>0.4208251069186318</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.001468513254418196</v>
+        <v>-4.264170270521672</v>
       </c>
       <c r="T23" t="n">
-        <v>2.688402749552169e-11</v>
+        <v>7.806403532105301e-08</v>
       </c>
       <c r="U23" t="n">
-        <v>0.001076188793124739</v>
+        <v>3.124964819557736</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.0004704898928226663</v>
+        <v>-1.366176987180268</v>
       </c>
       <c r="W23" t="n">
-        <v>2.314794541234433e-11</v>
+        <v>6.721545010263661e-08</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.060388636913086e-07</v>
+        <v>-0.0003079085385909591</v>
       </c>
       <c r="Y23" t="n">
-        <v>-4.892385509769198e-11</v>
+        <v>-1.420617731993698e-07</v>
       </c>
       <c r="Z23" t="n">
-        <v>0.0004808189587074771</v>
+        <v>1.396169835753984</v>
       </c>
     </row>
     <row r="24">
@@ -2179,79 +2179,79 @@
         <v>20</v>
       </c>
       <c r="B24" t="n">
-        <v>-9.655559792873063e-13</v>
+        <v>-5.234879557275676e-09</v>
       </c>
       <c r="C24" t="n">
-        <v>-8.057470188709985e-08</v>
+        <v>-0.0004368451752027207</v>
       </c>
       <c r="D24" t="n">
-        <v>5.085241912380446e-12</v>
+        <v>2.757023990283205e-08</v>
       </c>
       <c r="E24" t="n">
-        <v>6.162973216869097e-05</v>
+        <v>0.3341328049179761</v>
       </c>
       <c r="F24" t="n">
-        <v>7.220798136245825e-11</v>
+        <v>3.914840104546065e-07</v>
       </c>
       <c r="G24" t="n">
-        <v>-3.07365736483797e-12</v>
+        <v>-1.666418597236987e-08</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.001180442080402975</v>
+        <v>-6.399904875274338</v>
       </c>
       <c r="I24" t="n">
-        <v>1.593353320223658e-12</v>
+        <v>8.638552045441397e-09</v>
       </c>
       <c r="J24" t="n">
-        <v>3.687550404961869e-11</v>
+        <v>1.999248713984286e-07</v>
       </c>
       <c r="K24" t="n">
-        <v>3.751606776690781e-11</v>
+        <v>2.033977152519991e-07</v>
       </c>
       <c r="L24" t="n">
-        <v>-4.198718301370902e-11</v>
+        <v>-2.276384520219534e-07</v>
       </c>
       <c r="M24" t="n">
-        <v>-7.542680224915821e-08</v>
+        <v>-0.0004089352348989669</v>
       </c>
       <c r="N24" t="n">
-        <v>-6.162965287047329e-05</v>
+        <v>-0.3341323749934121</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.000396652836272448</v>
+        <v>-2.150499768514524</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.073837665958585e-12</v>
+        <v>-5.821937591024224e-09</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.0002137151343558305</v>
+        <v>1.158681610042978</v>
       </c>
       <c r="R24" t="n">
-        <v>0.0001432087740277948</v>
+        <v>0.7764231268082887</v>
       </c>
       <c r="S24" t="n">
-        <v>0.002258197424547894</v>
+        <v>12.24308159343352</v>
       </c>
       <c r="T24" t="n">
-        <v>4.324990214521171e-11</v>
+        <v>2.344844065066172e-07</v>
       </c>
       <c r="U24" t="n">
-        <v>0.0001821200519714422</v>
+        <v>0.9873851736117122</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.001149292961542862</v>
+        <v>-6.231026282276964</v>
       </c>
       <c r="W24" t="n">
-        <v>3.578844362388783e-11</v>
+        <v>1.940312353071732e-07</v>
       </c>
       <c r="X24" t="n">
-        <v>-7.542566917493702e-08</v>
+        <v>-0.000408929091813228</v>
       </c>
       <c r="Y24" t="n">
-        <v>-4.43754093095117e-11</v>
+        <v>-2.405865031186888e-07</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.972869981220092e-05</v>
+        <v>0.2153937951192237</v>
       </c>
     </row>
     <row r="25">
@@ -2259,79 +2259,79 @@
         <v>21</v>
       </c>
       <c r="B25" t="n">
-        <v>1.732614916544204e-11</v>
+        <v>5.397376838646966e-08</v>
       </c>
       <c r="C25" t="n">
-        <v>4.629676636120253e-08</v>
+        <v>0.0001442219772999522</v>
       </c>
       <c r="D25" t="n">
-        <v>1.357523168559616e-12</v>
+        <v>4.228899221863328e-09</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.991439400701757e-05</v>
+        <v>-0.09318821577676613</v>
       </c>
       <c r="F25" t="n">
-        <v>1.294513069515045e-11</v>
+        <v>4.032619874652065e-08</v>
       </c>
       <c r="G25" t="n">
-        <v>-6.753898685813904e-12</v>
+        <v>-2.103949053367866e-08</v>
       </c>
       <c r="H25" t="n">
-        <v>0.004017482738565584</v>
+        <v>12.51511390245764</v>
       </c>
       <c r="I25" t="n">
-        <v>-8.17742835077512e-13</v>
+        <v>-2.547401756944086e-09</v>
       </c>
       <c r="J25" t="n">
-        <v>2.118345719928625e-11</v>
+        <v>6.598996352927207e-08</v>
       </c>
       <c r="K25" t="n">
-        <v>-8.971938762096722e-12</v>
+        <v>-2.794899352456279e-08</v>
       </c>
       <c r="L25" t="n">
-        <v>-3.61856192005026e-11</v>
+        <v>-1.127240955960933e-07</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.529367099417941e-07</v>
+        <v>-0.0004764227924163026</v>
       </c>
       <c r="N25" t="n">
-        <v>2.991442141845224e-05</v>
+        <v>0.09318830116782487</v>
       </c>
       <c r="O25" t="n">
-        <v>-1.827002516542303e-05</v>
+        <v>-0.05691410786940435</v>
       </c>
       <c r="P25" t="n">
-        <v>-2.108499238157993e-13</v>
+        <v>-6.568280453186994e-10</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.0001716778327992827</v>
+        <v>0.5348044464223872</v>
       </c>
       <c r="R25" t="n">
-        <v>-9.155436209305126e-05</v>
+        <v>-0.2852067686221276</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.0005895967714217576</v>
+        <v>-1.836690094529033</v>
       </c>
       <c r="T25" t="n">
-        <v>1.227337007509586e-11</v>
+        <v>3.823355017870827e-08</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.000470085163715064</v>
+        <v>-1.464391946547633</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.0008729433636682573</v>
+        <v>-2.719360937591355</v>
       </c>
       <c r="W25" t="n">
-        <v>1.199785651577347e-11</v>
+        <v>3.737527271801365e-08</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.529276692054778e-07</v>
+        <v>-0.000476394629047881</v>
       </c>
       <c r="Y25" t="n">
-        <v>-6.407054832284201e-11</v>
+        <v>-1.995901722658303e-07</v>
       </c>
       <c r="Z25" t="n">
-        <v>-6.185328992452186e-05</v>
+        <v>-0.1926830851608319</v>
       </c>
     </row>
     <row r="26">
@@ -2339,79 +2339,79 @@
         <v>22</v>
       </c>
       <c r="B26" t="n">
-        <v>-1.075476334885993e-11</v>
+        <v>-2.272844014889158e-08</v>
       </c>
       <c r="C26" t="n">
-        <v>-3.140788077008786e-08</v>
+        <v>-6.63754373847869e-05</v>
       </c>
       <c r="D26" t="n">
-        <v>-1.670470594691949e-12</v>
+        <v>-3.530267558884836e-09</v>
       </c>
       <c r="E26" t="n">
-        <v>-5.779286237781277e-06</v>
+        <v>-0.01221357959847441</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.244926137538805e-11</v>
+        <v>-2.630948512366772e-08</v>
       </c>
       <c r="G26" t="n">
-        <v>4.87060761570016e-12</v>
+        <v>1.029323669054222e-08</v>
       </c>
       <c r="H26" t="n">
-        <v>0.0008090552127408229</v>
+        <v>1.709806338327673</v>
       </c>
       <c r="I26" t="n">
-        <v>4.317540969982439e-13</v>
+        <v>9.124410387791086e-10</v>
       </c>
       <c r="J26" t="n">
-        <v>-1.749322007010046e-11</v>
+        <v>-3.696906286356897e-08</v>
       </c>
       <c r="K26" t="n">
-        <v>8.300006769812941e-12</v>
+        <v>1.754073692015766e-08</v>
       </c>
       <c r="L26" t="n">
-        <v>2.186771826172074e-11</v>
+        <v>4.621386762522327e-08</v>
       </c>
       <c r="M26" t="n">
-        <v>1.07399229940449e-07</v>
+        <v>0.0002269707693546082</v>
       </c>
       <c r="N26" t="n">
-        <v>5.779261370941985e-06</v>
+        <v>0.01221352704645559</v>
       </c>
       <c r="O26" t="n">
-        <v>0.000335770841423145</v>
+        <v>0.7095969519138617</v>
       </c>
       <c r="P26" t="n">
-        <v>1.333039627907621e-13</v>
+        <v>2.817163657233168e-10</v>
       </c>
       <c r="Q26" t="n">
-        <v>-0.0005542102564591278</v>
+        <v>-1.171233055961511</v>
       </c>
       <c r="R26" t="n">
-        <v>0.0001578122972207451</v>
+        <v>0.3335105711018001</v>
       </c>
       <c r="S26" t="n">
-        <v>0.001983754769128991</v>
+        <v>4.192342406958894</v>
       </c>
       <c r="T26" t="n">
-        <v>-1.190222107779296e-11</v>
+        <v>-2.515340438447262e-08</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.0009043899456064271</v>
+        <v>-1.911280759293555</v>
       </c>
       <c r="V26" t="n">
-        <v>-0.0001107490050391306</v>
+        <v>-0.2340499731012143</v>
       </c>
       <c r="W26" t="n">
-        <v>-1.164538222162424e-11</v>
+        <v>-2.461061864763892e-08</v>
       </c>
       <c r="X26" t="n">
-        <v>1.073937188752223e-07</v>
+        <v>0.0002269591226116588</v>
       </c>
       <c r="Y26" t="n">
-        <v>3.143827519625169e-11</v>
+        <v>6.643966072131604e-08</v>
       </c>
       <c r="Z26" t="n">
-        <v>6.062703164717242e-05</v>
+        <v>0.1281253508436817</v>
       </c>
     </row>
     <row r="27">
@@ -2419,79 +2419,79 @@
         <v>23</v>
       </c>
       <c r="B27" t="n">
-        <v>2.43262690625813e-12</v>
+        <v>4.427034481217651e-09</v>
       </c>
       <c r="C27" t="n">
-        <v>-1.029393299436149e-08</v>
+        <v>-1.873348133731541e-05</v>
       </c>
       <c r="D27" t="n">
-        <v>4.471303599536801e-13</v>
+        <v>8.137141862385215e-10</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.0001670446406712071</v>
+        <v>-0.3039972826948101</v>
       </c>
       <c r="F27" t="n">
-        <v>1.135491320183095e-11</v>
+        <v>2.066431236030722e-08</v>
       </c>
       <c r="G27" t="n">
-        <v>-1.017757530945811e-12</v>
+        <v>-1.852172071157728e-09</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.0006009131768183886</v>
+        <v>-1.093575778033222</v>
       </c>
       <c r="I27" t="n">
-        <v>1.019836517052822e-13</v>
+        <v>1.855955446474743e-10</v>
       </c>
       <c r="J27" t="n">
-        <v>6.298235261538483e-12</v>
+        <v>1.146188312559637e-08</v>
       </c>
       <c r="K27" t="n">
-        <v>7.607911902149385e-12</v>
+        <v>1.384529929397335e-08</v>
       </c>
       <c r="L27" t="n">
-        <v>-1.346753067527133e-11</v>
+        <v>-2.450897975408428e-08</v>
       </c>
       <c r="M27" t="n">
-        <v>-2.644673649626369e-08</v>
+        <v>-4.812926651441153e-05</v>
       </c>
       <c r="N27" t="n">
-        <v>0.0001670446526869129</v>
+        <v>0.3039973045616733</v>
       </c>
       <c r="O27" t="n">
-        <v>-0.0002982075385270218</v>
+        <v>-0.5426949408676676</v>
       </c>
       <c r="P27" t="n">
-        <v>-2.22772959195272e-13</v>
+        <v>-4.054162462665626e-10</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.740798314190601e-05</v>
+        <v>0.0316800320625252</v>
       </c>
       <c r="R27" t="n">
-        <v>-0.0002441634336835903</v>
+        <v>-0.4443424229295819</v>
       </c>
       <c r="S27" t="n">
-        <v>0.0007355609327240714</v>
+        <v>1.338615377937843</v>
       </c>
       <c r="T27" t="n">
-        <v>6.153232788639e-12</v>
+        <v>1.119800056690556e-08</v>
       </c>
       <c r="U27" t="n">
-        <v>-6.58437165247778e-06</v>
+        <v>-0.01198261184891971</v>
       </c>
       <c r="V27" t="n">
-        <v>-8.026784614239616e-05</v>
+        <v>-0.1460759651851519</v>
       </c>
       <c r="W27" t="n">
-        <v>4.840253444072992e-12</v>
+        <v>8.808567829549199e-09</v>
       </c>
       <c r="X27" t="n">
-        <v>-2.644509151259388e-08</v>
+        <v>-4.812627288318538e-05</v>
       </c>
       <c r="Y27" t="n">
-        <v>-2.436932489445837e-11</v>
+        <v>-4.434866668262424e-08</v>
       </c>
       <c r="Z27" t="n">
-        <v>0.000524962979924801</v>
+        <v>0.9553573150941431</v>
       </c>
     </row>
     <row r="28">
@@ -2499,79 +2499,79 @@
         <v>24</v>
       </c>
       <c r="B28" t="n">
-        <v>-1.797981245987657e-12</v>
+        <v>-4.159464070795245e-09</v>
       </c>
       <c r="C28" t="n">
-        <v>-3.438127655386822e-08</v>
+        <v>-7.953790069572142e-05</v>
       </c>
       <c r="D28" t="n">
-        <v>2.009877226393435e-12</v>
+        <v>4.649665685165779e-09</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.0001015658682615151</v>
+        <v>-0.2349632344575978</v>
       </c>
       <c r="F28" t="n">
-        <v>2.693638578571549e-11</v>
+        <v>6.231483566619813e-08</v>
       </c>
       <c r="G28" t="n">
-        <v>-7.729060245671616e-13</v>
+        <v>-1.788046335105475e-09</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.0004453182901976943</v>
+        <v>-1.0302026420782</v>
       </c>
       <c r="I28" t="n">
-        <v>6.797910915858483e-13</v>
+        <v>1.572633081458579e-09</v>
       </c>
       <c r="J28" t="n">
-        <v>1.315566101092806e-11</v>
+        <v>3.043440216651209e-08</v>
       </c>
       <c r="K28" t="n">
-        <v>1.382925804702232e-11</v>
+        <v>3.199268850968134e-08</v>
       </c>
       <c r="L28" t="n">
-        <v>-1.235109294656376e-11</v>
+        <v>-2.857312538586147e-08</v>
       </c>
       <c r="M28" t="n">
-        <v>-1.881754279139051e-08</v>
+        <v>-4.353264334703628e-05</v>
       </c>
       <c r="N28" t="n">
-        <v>0.0001015658976183569</v>
+        <v>0.2349633023719351</v>
       </c>
       <c r="O28" t="n">
-        <v>0.000501781983339888</v>
+        <v>1.160826169422538</v>
       </c>
       <c r="P28" t="n">
-        <v>-3.804684760584773e-13</v>
+        <v>-8.801775518629809e-10</v>
       </c>
       <c r="Q28" t="n">
-        <v>-0.000117740007848554</v>
+        <v>-0.2723806091818954</v>
       </c>
       <c r="R28" t="n">
-        <v>8.243751928593626e-05</v>
+        <v>0.1907115697786398</v>
       </c>
       <c r="S28" t="n">
-        <v>0.0001371823488779957</v>
+        <v>0.3173586654117844</v>
       </c>
       <c r="T28" t="n">
-        <v>1.623899936021447e-11</v>
+        <v>3.756742101699206e-08</v>
       </c>
       <c r="U28" t="n">
-        <v>0.001231183395360272</v>
+        <v>2.848228816785988</v>
       </c>
       <c r="V28" t="n">
-        <v>-0.0006026071850047261</v>
+        <v>-1.394075940270872</v>
       </c>
       <c r="W28" t="n">
-        <v>1.347605620525834e-11</v>
+        <v>3.117560830144658e-08</v>
       </c>
       <c r="X28" t="n">
-        <v>-1.881790531030932e-08</v>
+        <v>-4.353348199432068e-05</v>
       </c>
       <c r="Y28" t="n">
-        <v>-8.665079818164205e-12</v>
+        <v>-2.00458855374383e-08</v>
       </c>
       <c r="Z28" t="n">
-        <v>-0.0004664795951642277</v>
+        <v>-1.079157362255221</v>
       </c>
     </row>
   </sheetData>
